--- a/downloads/result.xlsx
+++ b/downloads/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,11 @@
           <t>連結</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>【深層明細資料連結】</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -499,6 +504,11 @@
           <t>明細資料</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://carbonfee.moenv.gov.tw/front/reductionpublic/list/Detail?controlNo=B2313762</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -536,6 +546,11 @@
           <t>明細資料</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://carbonfee.moenv.gov.tw/front/reductionpublic/list/Detail?controlNo=B23D3224</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -575,6 +590,11 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>明細資料</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://carbonfee.moenv.gov.tw/front/reductionpublic/list/Detail?controlNo=B24A7498</t>
         </is>
       </c>
     </row>
@@ -614,6 +634,11 @@
           <t>明細資料</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://carbonfee.moenv.gov.tw/front/reductionpublic/list/Detail?controlNo=D32A0393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -651,6 +676,11 @@
           <t>明細資料</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://carbonfee.moenv.gov.tw/front/reductionpublic/list/Detail?controlNo=D9000120</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -688,6 +718,11 @@
           <t>明細資料</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://carbonfee.moenv.gov.tw/front/reductionpublic/list/Detail?controlNo=E1902497</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -727,6 +762,11 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>明細資料</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://carbonfee.moenv.gov.tw/front/reductionpublic/list/Detail?controlNo=E4901947</t>
         </is>
       </c>
     </row>
@@ -766,6 +806,11 @@
           <t>明細資料</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://carbonfee.moenv.gov.tw/front/reductionpublic/list/Detail?controlNo=E5600305</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -803,6 +848,11 @@
           <t>明細資料</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://carbonfee.moenv.gov.tw/front/reductionpublic/list/Detail?controlNo=E5600565</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -840,6 +890,11 @@
           <t>明細資料</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://carbonfee.moenv.gov.tw/front/reductionpublic/list/Detail?controlNo=E5600869</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
